--- a/scripts/Revenue forecast error math for US.xlsx
+++ b/scripts/Revenue forecast error math for US.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xabajian/Documents/GitHub/ACF_NK_Measurement/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE013DA-3D9D-EE45-9C1B-DF3692997FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBFEE69-5520-E74C-8A99-7D70C4D7CD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>GDP, forecast w error error</t>
   </si>
   <si>
-    <t>.0009 Case</t>
-  </si>
-  <si>
     <t>Sum of absolute values in column 3</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>Assumed Growth</t>
+  </si>
+  <si>
+    <t>.0010 Case (10 bps annually)</t>
   </si>
 </sst>
 </file>
@@ -95,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -134,7 +134,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -534,7 +534,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -542,13 +542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
@@ -557,10 +557,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -590,243 +590,235 @@
         <v>1.05</v>
       </c>
       <c r="C4" s="2">
-        <f>C3*B4</f>
+        <f t="shared" ref="C4:C13" si="0">C3*B4</f>
         <v>31.5</v>
       </c>
       <c r="D4" s="2">
-        <v>8.9999999999999998E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="E4" s="2">
-        <f>B4-D4</f>
-        <v>1.0491000000000001</v>
+        <f t="shared" ref="E4:E13" si="1">B4-D4</f>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F4" s="2">
         <f>F3*E4</f>
-        <v>31.473000000000006</v>
+        <v>31.470000000000006</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A12" si="0">A4+1</f>
+        <f t="shared" ref="A5:A12" si="2">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" ref="B5:B13" si="1">1.05</f>
+        <f t="shared" ref="B5:B13" si="3">1.05</f>
         <v>1.05</v>
       </c>
       <c r="C5" s="2">
-        <f>C4*B5</f>
+        <f t="shared" si="0"/>
         <v>33.075000000000003</v>
       </c>
       <c r="D5" s="2">
-        <f>D4</f>
-        <v>8.9999999999999998E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="E5" s="2">
-        <f>B5-D5</f>
-        <v>1.0491000000000001</v>
+        <f t="shared" si="1"/>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" ref="F5:F13" si="2">F4*E5</f>
-        <v>33.01832430000001</v>
+        <f t="shared" ref="F5:F13" si="4">F4*E5</f>
+        <v>33.01203000000001</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
+        <v>34.728750000000005</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E6" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C6" s="2">
-        <f>C5*B6</f>
-        <v>34.728750000000005</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" ref="D6:D13" si="3">D5</f>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E6" s="2">
-        <f>B6-D6</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="2"/>
-        <v>34.639524023130015</v>
+        <f t="shared" si="4"/>
+        <v>34.629619470000016</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B7" s="2">
+        <v>36.465187500000006</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E7" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C7" s="2">
-        <f>C6*B7</f>
-        <v>36.465187500000006</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E7" s="2">
-        <f>B7-D7</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="2"/>
-        <v>36.340324652665707</v>
+        <f t="shared" si="4"/>
+        <v>36.326470824030025</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
+        <v>38.288446875000005</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E8" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C8" s="2">
-        <f>C7*B8</f>
-        <v>38.288446875000005</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E8" s="2">
-        <f>B8-D8</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="2"/>
-        <v>38.124634593111601</v>
+        <f t="shared" si="4"/>
+        <v>38.106467894407501</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B9" s="2">
+        <v>40.20286921875001</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E9" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C9" s="2">
-        <f>C8*B9</f>
-        <v>40.20286921875001</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E9" s="2">
-        <f>B9-D9</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" si="2"/>
-        <v>39.996554151633383</v>
+        <f t="shared" si="4"/>
+        <v>39.973684821233476</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
+        <v>42.213012679687509</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E10" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C10" s="2">
-        <f>C9*B10</f>
-        <v>42.213012679687509</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E10" s="2">
-        <f>B10-D10</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="2"/>
-        <v>41.960384960478585</v>
+        <f t="shared" si="4"/>
+        <v>41.932395377473924</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B11" s="2">
+        <v>44.323663313671886</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E11" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C11" s="2">
-        <f>C10*B11</f>
-        <v>44.323663313671886</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E11" s="2">
-        <f>B11-D11</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="2"/>
-        <v>44.020639862038088</v>
+        <f t="shared" si="4"/>
+        <v>43.987082750970153</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C12" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B12" s="2">
+        <v>46.539846479355482</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E12" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C12" s="2">
-        <f>C11*B12</f>
-        <v>46.539846479355482</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E12" s="2">
-        <f>B12-D12</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="2"/>
-        <v>46.182053279264167</v>
+        <f t="shared" si="4"/>
+        <v>46.142449805767697</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -836,24 +828,23 @@
         <v>10</v>
       </c>
       <c r="B13" s="2">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="0"/>
+        <v>48.866838803323262</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="E13" s="2">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="C13" s="2">
-        <f>C12*B13</f>
-        <v>48.866838803323262</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="E13" s="2">
-        <f>B13-D13</f>
-        <v>1.0491000000000001</v>
+        <v>1.0490000000000002</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="2"/>
-        <v>48.449592095276046</v>
+        <f t="shared" si="4"/>
+        <v>48.403429846250319</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -871,39 +862,39 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2">
         <f>SUM(F4:F13)</f>
-        <v>394.20503191759764</v>
+        <v>393.98363079013313</v>
       </c>
       <c r="G14" s="2">
         <f>C14-F14</f>
-        <v>1.9985829521905885</v>
+        <v>2.2199840796550916</v>
       </c>
       <c r="H14" s="2">
         <f>G14*0.2</f>
-        <v>0.39971659043811769</v>
+        <v>0.44399681593101836</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
         <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
         <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -918,7 +909,7 @@
   <sheetData>
     <row r="19" spans="14:14">
       <c r="N19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="14:14" ht="18">

--- a/scripts/Revenue forecast error math for US.xlsx
+++ b/scripts/Revenue forecast error math for US.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xabajian/Documents/GitHub/ACF_NK_Measurement/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBFEE69-5520-E74C-8A99-7D70C4D7CD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD34253B-1CB9-DF44-B230-64DA2550458C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
+    <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
   </bookViews>
   <sheets>
     <sheet name="RMSE Version" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Year</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Dif ($Trillions)</t>
   </si>
   <si>
-    <t xml:space="preserve">Delta revenues </t>
-  </si>
-  <si>
     <t>Step 1</t>
   </si>
   <si>
@@ -75,29 +72,63 @@
     <t>Sum the forecast error to get cumulative error in GDP over 10 years</t>
   </si>
   <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Assume tax revenues are 1/5 of GDP to arrive at ~approximate~ forecast error in government revenue terms</t>
-  </si>
-  <si>
     <t>GDP, true DGP, $T$</t>
   </si>
   <si>
     <t>Assumed Growth</t>
   </si>
   <si>
-    <t>.0010 Case (10 bps annually)</t>
+    <t>Cost of  CAAA between 1970 and 1990</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/A191RD3A086NBEA</t>
+  </si>
+  <si>
+    <t>Step 3</t>
+  </si>
+  <si>
+    <t>Inflate cumulative cost of CAAA between 1970 and 1990 to 2025 dollars using</t>
+  </si>
+  <si>
+    <t>GDP Price 1990</t>
+  </si>
+  <si>
+    <t>.00656 Case (order 7 bps annually)</t>
+  </si>
+  <si>
+    <t>GDP Price 2025</t>
+  </si>
+  <si>
+    <t>CAAA cost $2025</t>
+  </si>
+  <si>
+    <t>Difference in Revenues</t>
+  </si>
+  <si>
+    <t>deflator</t>
+  </si>
+  <si>
+    <t>caaa cost</t>
+  </si>
+  <si>
+    <t>https://www.epa.gov/sites/default/files/2015-06/documents/contsetc.pdf</t>
+  </si>
+  <si>
+    <t>Ratio FE to cost</t>
+  </si>
+  <si>
+    <t>Ratio revenue FE to cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -109,6 +140,11 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="-webkit-standard"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF141413"/>
+      <name val="Times"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,11 +167,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352FBFC7-236B-8E46-85A4-04D79EF549E8}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -529,23 +567,25 @@
     <col min="5" max="5" width="24.33203125" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -560,10 +600,13 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -580,7 +623,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>1</v>
@@ -593,21 +636,21 @@
         <f t="shared" ref="C4:C13" si="0">C3*B4</f>
         <v>31.5</v>
       </c>
-      <c r="D4" s="2">
-        <v>1E-3</v>
+      <c r="D4" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E13" si="1">B4-D4</f>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F4" s="2">
         <f>F3*E4</f>
-        <v>31.470000000000006</v>
+        <v>31.480308000000001</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A12" si="2">A4+1</f>
         <v>2</v>
@@ -620,21 +663,21 @@
         <f t="shared" si="0"/>
         <v>33.075000000000003</v>
       </c>
-      <c r="D5" s="2">
-        <v>1E-3</v>
+      <c r="D5" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" ref="F5:F13" si="4">F4*E5</f>
-        <v>33.01203000000001</v>
+        <v>33.033659725828805</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -647,21 +690,21 @@
         <f t="shared" si="0"/>
         <v>34.728750000000005</v>
       </c>
-      <c r="D6" s="2">
-        <v>1E-3</v>
+      <c r="D6" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="4"/>
-        <v>34.629619470000016</v>
+        <v>34.663659417876211</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -674,21 +717,21 @@
         <f t="shared" si="0"/>
         <v>36.465187500000006</v>
       </c>
-      <c r="D7" s="2">
-        <v>1E-3</v>
+      <c r="D7" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="4"/>
-        <v>36.326470824030025</v>
+        <v>36.374089162728126</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -701,21 +744,21 @@
         <f t="shared" si="0"/>
         <v>38.288446875000005</v>
       </c>
-      <c r="D8" s="2">
-        <v>1E-3</v>
+      <c r="D8" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="4"/>
-        <v>38.106467894407501</v>
+        <v>38.168917668738118</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -728,21 +771,21 @@
         <f t="shared" si="0"/>
         <v>40.20286921875001</v>
       </c>
-      <c r="D9" s="2">
-        <v>1E-3</v>
+      <c r="D9" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="4"/>
-        <v>39.973684821233476</v>
+        <v>40.052309474617267</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -755,21 +798,21 @@
         <f t="shared" si="0"/>
         <v>42.213012679687509</v>
       </c>
-      <c r="D10" s="2">
-        <v>1E-3</v>
+      <c r="D10" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="4"/>
-        <v>41.932395377473924</v>
+        <v>42.028634612408993</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -782,21 +825,21 @@
         <f t="shared" si="0"/>
         <v>44.323663313671886</v>
       </c>
-      <c r="D11" s="2">
-        <v>1E-3</v>
+      <c r="D11" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="4"/>
-        <v>43.987082750970153</v>
+        <v>44.102478747269856</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -809,21 +852,24 @@
         <f t="shared" si="0"/>
         <v>46.539846479355482</v>
       </c>
-      <c r="D12" s="2">
-        <v>1E-3</v>
+      <c r="D12" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="4"/>
-        <v>46.142449805767697</v>
+        <v>46.278653817583645</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="L12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -835,21 +881,27 @@
         <f t="shared" si="0"/>
         <v>48.866838803323262</v>
       </c>
-      <c r="D13" s="2">
-        <v>1E-3</v>
+      <c r="D13" s="4">
+        <v>6.5640000000000002E-4</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="1"/>
-        <v>1.0490000000000002</v>
+        <v>1.0493436</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="4"/>
-        <v>48.403429846250319</v>
+        <v>48.562209200096966</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13">
+        <v>59.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -862,39 +914,89 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2">
         <f>SUM(F4:F13)</f>
-        <v>393.98363079013313</v>
+        <v>394.74491982714795</v>
       </c>
       <c r="G14" s="2">
         <f>C14-F14</f>
-        <v>2.2199840796550916</v>
+        <v>1.4586950426402723</v>
       </c>
       <c r="H14" s="2">
         <f>G14*0.2</f>
-        <v>0.44399681593101836</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>0.29173900852805446</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14">
+        <v>128.98599999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="L15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15">
+        <f>I14*M14/M13</f>
+        <v>1.1428032864645095</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16">
+        <f>H14/M15</f>
+        <v>0.2552836625370648</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17">
+        <f>H14/G14</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/Revenue forecast error math for US.xlsx
+++ b/scripts/Revenue forecast error math for US.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xabajian/Documents/GitHub/ACF_NK_Measurement/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD34253B-1CB9-DF44-B230-64DA2550458C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF02386-A3A0-FE4A-98B5-7155843E52E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -172,7 +172,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -640,23 +640,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E4" s="2">
-        <f t="shared" ref="E4:E13" si="1">B4-D4</f>
-        <v>1.0493436</v>
+        <f>B4+D4</f>
+        <v>1.0506564</v>
       </c>
       <c r="F4" s="2">
         <f>F3*E4</f>
-        <v>31.480308000000001</v>
+        <v>31.519692000000003</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A12" si="2">A4+1</f>
+        <f t="shared" ref="A5:A12" si="1">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" ref="B5:B13" si="3">1.05</f>
+        <f t="shared" ref="B5:B13" si="2">1.05</f>
         <v>1.05</v>
       </c>
       <c r="C5" s="2">
@@ -667,23 +667,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E5" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" ref="E5:E13" si="3">B5+D5</f>
+        <v>1.0506564</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" ref="F5:F13" si="4">F4*E5</f>
-        <v>33.033659725828805</v>
+        <v>33.116366125828804</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="3">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C6" s="2">
@@ -694,23 +694,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="4"/>
-        <v>34.663659417876211</v>
+        <v>34.793922014845243</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="B7" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C7" s="2">
@@ -721,23 +721,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="4"/>
-        <v>36.374089162728126</v>
+        <v>36.556456845998049</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C8" s="2">
@@ -748,23 +748,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="4"/>
-        <v>38.168917668738118</v>
+        <v>38.408275346571664</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="B9" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C9" s="2">
@@ -775,23 +775,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E9" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="4"/>
-        <v>40.052309474617267</v>
+        <v>40.35390030583774</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="3">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
         <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C10" s="2">
@@ -802,23 +802,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="4"/>
-        <v>42.028634612408993</v>
+        <v>42.398083621290382</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="B11" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C11" s="2">
@@ -829,23 +829,23 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E11" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="4"/>
-        <v>44.102478747269856</v>
+        <v>44.545817904443922</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="B12" s="2">
-        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="C12" s="2">
@@ -856,12 +856,12 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="4"/>
-        <v>46.278653817583645</v>
+        <v>46.802348674538599</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.05</v>
       </c>
       <c r="C13" s="2">
@@ -885,12 +885,12 @@
         <v>6.5640000000000002E-4</v>
       </c>
       <c r="E13" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0493436</v>
+        <f t="shared" si="3"/>
+        <v>1.0506564</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="4"/>
-        <v>48.562209200096966</v>
+        <v>49.173187169935495</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -914,15 +914,15 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2">
         <f>SUM(F4:F13)</f>
-        <v>394.74491982714795</v>
+        <v>397.66805000928991</v>
       </c>
       <c r="G14" s="2">
         <f>C14-F14</f>
-        <v>1.4586950426402723</v>
+        <v>-1.4644351395016884</v>
       </c>
       <c r="H14" s="2">
         <f>G14*0.2</f>
-        <v>0.29173900852805446</v>
+        <v>-0.29288702790033766</v>
       </c>
       <c r="I14" s="5">
         <v>0.52300000000000002</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="M16">
         <f>H14/M15</f>
-        <v>0.2552836625370648</v>
+        <v>-0.25628822682724534</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -964,7 +964,7 @@
       </c>
       <c r="M17">
         <f>H14/G14</f>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:13">

--- a/scripts/Revenue forecast error math for US.xlsx
+++ b/scripts/Revenue forecast error math for US.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF02386-A3A0-FE4A-98B5-7155843E52E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
+    <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
   </bookViews>
   <sheets>
     <sheet name="RMSE Version" sheetId="1" r:id="rId1"/>

--- a/scripts/Revenue forecast error math for US.xlsx
+++ b/scripts/Revenue forecast error math for US.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xabajian/Documents/GitHub/ACF_NK_Measurement/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF02386-A3A0-FE4A-98B5-7155843E52E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5234BD23-63B7-994C-92F4-8858CDBAF939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
+    <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
   </bookViews>
   <sheets>
     <sheet name="RMSE Version" sheetId="1" r:id="rId1"/>
@@ -637,15 +637,15 @@
         <v>31.5</v>
       </c>
       <c r="D4" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E4" s="2">
         <f>B4+D4</f>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F4" s="2">
         <f>F3*E4</f>
-        <v>31.519692000000003</v>
+        <v>31.521890432999999</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -664,15 +664,15 @@
         <v>33.075000000000003</v>
       </c>
       <c r="D5" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" ref="E5:E13" si="3">B5+D5</f>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" ref="F5:F13" si="4">F4*E5</f>
-        <v>33.116366125828804</v>
+        <v>33.120985882335226</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -691,15 +691,15 @@
         <v>34.728750000000005</v>
       </c>
       <c r="D6" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="4"/>
-        <v>34.793922014845243</v>
+        <v>34.801202933863692</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -718,15 +718,15 @@
         <v>36.465187500000006</v>
       </c>
       <c r="D7" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="4"/>
-        <v>36.556456845998049</v>
+        <v>36.566656860594982</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -745,15 +745,15 @@
         <v>38.288446875000005</v>
       </c>
       <c r="D8" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="4"/>
-        <v>38.408275346571664</v>
+        <v>38.421671702026089</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -772,15 +772,15 @@
         <v>40.20286921875001</v>
       </c>
       <c r="D9" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="4"/>
-        <v>40.35390030583774</v>
+        <v>40.370790854798763</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -799,15 +799,15 @@
         <v>42.213012679687509</v>
       </c>
       <c r="D10" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="4"/>
-        <v>42.398083621290382</v>
+        <v>42.418788200617499</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -826,15 +826,15 @@
         <v>44.323663313671886</v>
       </c>
       <c r="D11" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="4"/>
-        <v>44.545817904443922</v>
+        <v>44.570679798683265</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -853,15 +853,15 @@
         <v>46.539846479355482</v>
       </c>
       <c r="D12" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="4"/>
-        <v>46.802348674538599</v>
+        <v>46.831736171280681</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -882,15 +882,15 @@
         <v>48.866838803323262</v>
       </c>
       <c r="D13" s="4">
-        <v>6.5640000000000002E-4</v>
+        <v>7.2968109999999996E-4</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="3"/>
-        <v>1.0506564</v>
+        <v>1.0507296811</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="4"/>
-        <v>49.173187169935495</v>
+        <v>49.207495212609082</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -914,15 +914,15 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2">
         <f>SUM(F4:F13)</f>
-        <v>397.66805000928991</v>
+        <v>397.8318980498093</v>
       </c>
       <c r="G14" s="2">
         <f>C14-F14</f>
-        <v>-1.4644351395016884</v>
+        <v>-1.6282831800210715</v>
       </c>
       <c r="H14" s="2">
         <f>G14*0.2</f>
-        <v>-0.29288702790033766</v>
+        <v>-0.32565663600421435</v>
       </c>
       <c r="I14" s="5">
         <v>0.52300000000000002</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="M16">
         <f>H14/M15</f>
-        <v>-0.25628822682724534</v>
+        <v>-0.28496298519730223</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -964,7 +964,7 @@
       </c>
       <c r="M17">
         <f>H14/G14</f>
-        <v>0.19999999999999998</v>
+        <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:13">
